--- a/data/nzd0267/nzd0267.xlsx
+++ b/data/nzd0267/nzd0267.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y389"/>
+  <dimension ref="A1:Y391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31963,6 +31963,168 @@
         <v>274.55</v>
       </c>
       <c r="Y389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:54:22+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>298.41</v>
+      </c>
+      <c r="C390" t="n">
+        <v>272.74</v>
+      </c>
+      <c r="D390" t="n">
+        <v>262.22</v>
+      </c>
+      <c r="E390" t="n">
+        <v>248.99</v>
+      </c>
+      <c r="F390" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="G390" t="n">
+        <v>248.69</v>
+      </c>
+      <c r="H390" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="I390" t="n">
+        <v>292.08</v>
+      </c>
+      <c r="J390" t="n">
+        <v>289.58</v>
+      </c>
+      <c r="K390" t="n">
+        <v>290.49</v>
+      </c>
+      <c r="L390" t="n">
+        <v>290.15</v>
+      </c>
+      <c r="M390" t="n">
+        <v>284.88</v>
+      </c>
+      <c r="N390" t="n">
+        <v>280.63</v>
+      </c>
+      <c r="O390" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="P390" t="n">
+        <v>292.76</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="R390" t="n">
+        <v>291.46</v>
+      </c>
+      <c r="S390" t="n">
+        <v>293.15</v>
+      </c>
+      <c r="T390" t="n">
+        <v>273.39</v>
+      </c>
+      <c r="U390" t="n">
+        <v>255.72</v>
+      </c>
+      <c r="V390" t="n">
+        <v>232.59</v>
+      </c>
+      <c r="W390" t="n">
+        <v>248.18</v>
+      </c>
+      <c r="X390" t="n">
+        <v>275.57</v>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>299.56</v>
+      </c>
+      <c r="C391" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="D391" t="n">
+        <v>261.14</v>
+      </c>
+      <c r="E391" t="n">
+        <v>249.54</v>
+      </c>
+      <c r="F391" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="G391" t="n">
+        <v>249.46</v>
+      </c>
+      <c r="H391" t="n">
+        <v>268.97</v>
+      </c>
+      <c r="I391" t="n">
+        <v>293.12</v>
+      </c>
+      <c r="J391" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="K391" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="L391" t="n">
+        <v>290.22</v>
+      </c>
+      <c r="M391" t="n">
+        <v>285.23</v>
+      </c>
+      <c r="N391" t="n">
+        <v>280.82</v>
+      </c>
+      <c r="O391" t="n">
+        <v>297.41</v>
+      </c>
+      <c r="P391" t="n">
+        <v>293.09</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>286.44</v>
+      </c>
+      <c r="R391" t="n">
+        <v>291.77</v>
+      </c>
+      <c r="S391" t="n">
+        <v>293.32</v>
+      </c>
+      <c r="T391" t="n">
+        <v>273.54</v>
+      </c>
+      <c r="U391" t="n">
+        <v>256.51</v>
+      </c>
+      <c r="V391" t="n">
+        <v>231.86</v>
+      </c>
+      <c r="W391" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="X391" t="n">
+        <v>276.39</v>
+      </c>
+      <c r="Y391" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31979,7 +32141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B390"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35882,6 +36044,26 @@
       </c>
       <c r="B390" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -36050,28 +36232,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7579230587998373</v>
+        <v>-0.7547812499603536</v>
       </c>
       <c r="J2" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K2" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2587450124458262</v>
+        <v>0.2593971484102214</v>
       </c>
       <c r="M2" t="n">
-        <v>7.303631468856502</v>
+        <v>7.281690312376682</v>
       </c>
       <c r="N2" t="n">
-        <v>90.61630722450309</v>
+        <v>90.19786725030393</v>
       </c>
       <c r="O2" t="n">
-        <v>9.519259804443992</v>
+        <v>9.497255774712183</v>
       </c>
       <c r="P2" t="n">
-        <v>315.9262154619481</v>
+        <v>315.8948234149935</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36128,28 +36310,28 @@
         <v>0.0786</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3283913023373655</v>
+        <v>-0.3224024072607645</v>
       </c>
       <c r="J3" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K3" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07443762918755004</v>
+        <v>0.07261174526023673</v>
       </c>
       <c r="M3" t="n">
-        <v>6.761188518440796</v>
+        <v>6.752358922348738</v>
       </c>
       <c r="N3" t="n">
-        <v>73.83409017698216</v>
+        <v>73.61819209456843</v>
       </c>
       <c r="O3" t="n">
-        <v>8.592676543253688</v>
+        <v>8.580104433779837</v>
       </c>
       <c r="P3" t="n">
-        <v>276.1348047354834</v>
+        <v>276.0749687594177</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36206,28 +36388,28 @@
         <v>0.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03639666434354519</v>
+        <v>-0.02897020900221351</v>
       </c>
       <c r="J4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005332674966203044</v>
+        <v>0.0003414414444867786</v>
       </c>
       <c r="M4" t="n">
-        <v>9.143699053205946</v>
+        <v>9.133593011285864</v>
       </c>
       <c r="N4" t="n">
-        <v>136.7120749451715</v>
+        <v>136.2613196038633</v>
       </c>
       <c r="O4" t="n">
-        <v>11.69239389283356</v>
+        <v>11.6731023984142</v>
       </c>
       <c r="P4" t="n">
-        <v>255.6078916198179</v>
+        <v>255.533698063488</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36284,28 +36466,28 @@
         <v>0.0537</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004155281942167987</v>
+        <v>0.006255600072617776</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K5" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L5" t="n">
-        <v>8.699723252902913e-08</v>
+        <v>1.993078490980515e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.746214806445033</v>
+        <v>7.729718664045858</v>
       </c>
       <c r="N5" t="n">
-        <v>109.2838526246963</v>
+        <v>108.8776588944229</v>
       </c>
       <c r="O5" t="n">
-        <v>10.45389174540737</v>
+        <v>10.43444578760285</v>
       </c>
       <c r="P5" t="n">
-        <v>243.7285995318473</v>
+        <v>243.6702511843582</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36362,28 +36544,28 @@
         <v>0.1262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08492662963952226</v>
+        <v>0.08692501064207292</v>
       </c>
       <c r="J6" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K6" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01005975287277328</v>
+        <v>0.01065604073657678</v>
       </c>
       <c r="M6" t="n">
-        <v>4.961672142092036</v>
+        <v>4.943967206817641</v>
       </c>
       <c r="N6" t="n">
-        <v>39.0813831852162</v>
+        <v>38.90225888128934</v>
       </c>
       <c r="O6" t="n">
-        <v>6.251510472295172</v>
+        <v>6.23716753673407</v>
       </c>
       <c r="P6" t="n">
-        <v>242.1812054462375</v>
+        <v>242.161236087472</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36440,28 +36622,28 @@
         <v>0.0742</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06564297712101094</v>
+        <v>-0.06944878626820485</v>
       </c>
       <c r="J7" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K7" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008279451849228958</v>
+        <v>0.009349271179231344</v>
       </c>
       <c r="M7" t="n">
-        <v>4.188521168845051</v>
+        <v>4.185729494803578</v>
       </c>
       <c r="N7" t="n">
-        <v>28.42004388987351</v>
+        <v>28.34040204850245</v>
       </c>
       <c r="O7" t="n">
-        <v>5.331045290547953</v>
+        <v>5.323570422987044</v>
       </c>
       <c r="P7" t="n">
-        <v>254.4000715421901</v>
+        <v>254.4380927338846</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36518,28 +36700,28 @@
         <v>0.0602</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08012100938892203</v>
+        <v>-0.08275214064200997</v>
       </c>
       <c r="J8" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K8" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008320512577785322</v>
+        <v>0.008972104204664211</v>
       </c>
       <c r="M8" t="n">
-        <v>5.05771726404532</v>
+        <v>5.044948432310064</v>
       </c>
       <c r="N8" t="n">
-        <v>42.12835981020893</v>
+        <v>41.94535984778406</v>
       </c>
       <c r="O8" t="n">
-        <v>6.490636317820383</v>
+        <v>6.476523747179814</v>
       </c>
       <c r="P8" t="n">
-        <v>272.9732731034285</v>
+        <v>272.9995572942521</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36596,28 +36778,28 @@
         <v>0.0639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2183253030762002</v>
+        <v>0.212295583212005</v>
       </c>
       <c r="J9" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K9" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05038811128125464</v>
+        <v>0.04817923034589711</v>
       </c>
       <c r="M9" t="n">
-        <v>5.523936205634722</v>
+        <v>5.522984013938537</v>
       </c>
       <c r="N9" t="n">
-        <v>49.46370974745307</v>
+        <v>49.37545573631365</v>
       </c>
       <c r="O9" t="n">
-        <v>7.03304413091892</v>
+        <v>7.026767089943543</v>
       </c>
       <c r="P9" t="n">
-        <v>292.5650958132449</v>
+        <v>292.62533498943</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36674,28 +36856,28 @@
         <v>0.066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2979496936559673</v>
+        <v>0.2901377021539784</v>
       </c>
       <c r="J10" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K10" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09907386591076761</v>
+        <v>0.09494407667824711</v>
       </c>
       <c r="M10" t="n">
-        <v>5.287059819256908</v>
+        <v>5.296921230806309</v>
       </c>
       <c r="N10" t="n">
-        <v>44.55703666478239</v>
+        <v>44.60464069822881</v>
       </c>
       <c r="O10" t="n">
-        <v>6.675105741842775</v>
+        <v>6.678670578657763</v>
       </c>
       <c r="P10" t="n">
-        <v>289.4691020739496</v>
+        <v>289.547082176594</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36752,28 +36934,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3006162101267954</v>
+        <v>0.2963778705127635</v>
       </c>
       <c r="J11" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K11" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1819668370118747</v>
+        <v>0.1790214817219563</v>
       </c>
       <c r="M11" t="n">
-        <v>3.657691688456319</v>
+        <v>3.659825838271762</v>
       </c>
       <c r="N11" t="n">
-        <v>22.36989435723276</v>
+        <v>22.33840049588155</v>
       </c>
       <c r="O11" t="n">
-        <v>4.729682268105623</v>
+        <v>4.726351710979786</v>
       </c>
       <c r="P11" t="n">
-        <v>287.255472166824</v>
+        <v>287.2978133704005</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36830,28 +37012,28 @@
         <v>0.0518</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2600898637210016</v>
+        <v>0.2586327044627477</v>
       </c>
       <c r="J12" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K12" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L12" t="n">
-        <v>0.226538036539699</v>
+        <v>0.2265773615391833</v>
       </c>
       <c r="M12" t="n">
-        <v>2.77764342238167</v>
+        <v>2.770920520698413</v>
       </c>
       <c r="N12" t="n">
-        <v>12.71760001444797</v>
+        <v>12.66196554138538</v>
       </c>
       <c r="O12" t="n">
-        <v>3.566174422886235</v>
+        <v>3.558365571633328</v>
       </c>
       <c r="P12" t="n">
-        <v>284.7304155986495</v>
+        <v>284.7449736248084</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36908,28 +37090,28 @@
         <v>0.0463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.275433833173617</v>
+        <v>0.2765635967015257</v>
       </c>
       <c r="J13" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K13" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2231131239023388</v>
+        <v>0.2265984792188139</v>
       </c>
       <c r="M13" t="n">
-        <v>2.862147057833367</v>
+        <v>2.852416672661714</v>
       </c>
       <c r="N13" t="n">
-        <v>14.54546865059937</v>
+        <v>14.47677885478623</v>
       </c>
       <c r="O13" t="n">
-        <v>3.813852206182008</v>
+        <v>3.804836245462639</v>
       </c>
       <c r="P13" t="n">
-        <v>276.7510148049907</v>
+        <v>276.7397267352391</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36986,28 +37168,28 @@
         <v>0.0502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2944176101425524</v>
+        <v>0.2989322082728896</v>
       </c>
       <c r="J14" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K14" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1531622304864071</v>
+        <v>0.1583101696787657</v>
       </c>
       <c r="M14" t="n">
-        <v>4.062893383252663</v>
+        <v>4.06457549458163</v>
       </c>
       <c r="N14" t="n">
-        <v>26.38982934643408</v>
+        <v>26.34647797247764</v>
       </c>
       <c r="O14" t="n">
-        <v>5.137103205740963</v>
+        <v>5.132882033758192</v>
       </c>
       <c r="P14" t="n">
-        <v>268.716402842003</v>
+        <v>268.6712979496057</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37064,28 +37246,28 @@
         <v>0.0561</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1659848431977552</v>
+        <v>0.1662503795323594</v>
       </c>
       <c r="J15" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K15" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1113852470113084</v>
+        <v>0.1129124876072238</v>
       </c>
       <c r="M15" t="n">
-        <v>2.516867964439033</v>
+        <v>2.505686340219579</v>
       </c>
       <c r="N15" t="n">
-        <v>12.10272569613504</v>
+        <v>12.04158515397538</v>
       </c>
       <c r="O15" t="n">
-        <v>3.478897195396127</v>
+        <v>3.4700987239523</v>
       </c>
       <c r="P15" t="n">
-        <v>292.4562910684197</v>
+        <v>292.4536364573439</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37142,28 +37324,28 @@
         <v>0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1224620977344923</v>
+        <v>0.1215178708078947</v>
       </c>
       <c r="J16" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K16" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06773521227045365</v>
+        <v>0.06750634868283212</v>
       </c>
       <c r="M16" t="n">
-        <v>2.45870929997576</v>
+        <v>2.450907805910064</v>
       </c>
       <c r="N16" t="n">
-        <v>11.36550276742026</v>
+        <v>11.31137624552005</v>
       </c>
       <c r="O16" t="n">
-        <v>3.371276133368529</v>
+        <v>3.36323895159414</v>
       </c>
       <c r="P16" t="n">
-        <v>290.5985844703959</v>
+        <v>290.6080172543359</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37220,28 +37402,28 @@
         <v>0.0537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09048584552008114</v>
+        <v>0.08926204098943429</v>
       </c>
       <c r="J17" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K17" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02804816060922888</v>
+        <v>0.0276290527765074</v>
       </c>
       <c r="M17" t="n">
-        <v>2.890665224148267</v>
+        <v>2.881329012336432</v>
       </c>
       <c r="N17" t="n">
-        <v>15.62291739481649</v>
+        <v>15.55011067137002</v>
       </c>
       <c r="O17" t="n">
-        <v>3.952583635398053</v>
+        <v>3.943362863264046</v>
       </c>
       <c r="P17" t="n">
-        <v>285.5522061761582</v>
+        <v>285.5644345817005</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37298,28 +37480,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06275612931913278</v>
+        <v>0.06380962243609109</v>
       </c>
       <c r="J18" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K18" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01007871580236175</v>
+        <v>0.01054043629429025</v>
       </c>
       <c r="M18" t="n">
-        <v>3.055480296354952</v>
+        <v>3.044709891418046</v>
       </c>
       <c r="N18" t="n">
-        <v>21.31318433032678</v>
+        <v>21.20874354091325</v>
       </c>
       <c r="O18" t="n">
-        <v>4.616620444689684</v>
+        <v>4.605295163278164</v>
       </c>
       <c r="P18" t="n">
-        <v>288.9682047347799</v>
+        <v>288.9576718141894</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37376,28 +37558,28 @@
         <v>0.0365</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.09101668540489338</v>
+        <v>-0.08931358405519979</v>
       </c>
       <c r="J19" t="n">
+        <v>390</v>
+      </c>
+      <c r="K19" t="n">
         <v>388</v>
       </c>
-      <c r="K19" t="n">
-        <v>386</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0122319281447546</v>
+        <v>0.01192378538317485</v>
       </c>
       <c r="M19" t="n">
-        <v>3.931734091179138</v>
+        <v>3.91839374966982</v>
       </c>
       <c r="N19" t="n">
-        <v>36.2668136184041</v>
+        <v>36.09269467589971</v>
       </c>
       <c r="O19" t="n">
-        <v>6.022193422533363</v>
+        <v>6.007719590318752</v>
       </c>
       <c r="P19" t="n">
-        <v>294.0393328432099</v>
+        <v>294.0221147441077</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37454,28 +37636,28 @@
         <v>0.0659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1375951633572794</v>
+        <v>-0.1359630430900772</v>
       </c>
       <c r="J20" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K20" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1135301891280466</v>
+        <v>0.1122141539305703</v>
       </c>
       <c r="M20" t="n">
-        <v>2.223620956494989</v>
+        <v>2.220248401655631</v>
       </c>
       <c r="N20" t="n">
-        <v>8.159419515744053</v>
+        <v>8.129549904514747</v>
       </c>
       <c r="O20" t="n">
-        <v>2.856469764542249</v>
+        <v>2.851236557094964</v>
       </c>
       <c r="P20" t="n">
-        <v>275.5365182445265</v>
+        <v>275.5202255577926</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37532,28 +37714,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.08230379891582128</v>
+        <v>-0.07211351490473358</v>
       </c>
       <c r="J21" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K21" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02105866460560957</v>
+        <v>0.01601384659014826</v>
       </c>
       <c r="M21" t="n">
-        <v>3.336210087127649</v>
+        <v>3.369538537899137</v>
       </c>
       <c r="N21" t="n">
-        <v>17.38064702745817</v>
+        <v>17.76195735440307</v>
       </c>
       <c r="O21" t="n">
-        <v>4.169010317504404</v>
+        <v>4.214493724565629</v>
       </c>
       <c r="P21" t="n">
-        <v>248.6344186696195</v>
+        <v>248.5326941880743</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37610,28 +37792,28 @@
         <v>0.1216</v>
       </c>
       <c r="I22" t="n">
-        <v>0.203930905265902</v>
+        <v>0.2085009532655642</v>
       </c>
       <c r="J22" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K22" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L22" t="n">
-        <v>0.07998122473307678</v>
+        <v>0.08396256382517298</v>
       </c>
       <c r="M22" t="n">
-        <v>3.957111073764276</v>
+        <v>3.962604160464777</v>
       </c>
       <c r="N22" t="n">
-        <v>26.40432515584499</v>
+        <v>26.36378688295678</v>
       </c>
       <c r="O22" t="n">
-        <v>5.138513905385972</v>
+        <v>5.134567837993455</v>
       </c>
       <c r="P22" t="n">
-        <v>222.5426550212036</v>
+        <v>222.4970372282931</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37688,28 +37870,28 @@
         <v>0.0709</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3390112861474657</v>
+        <v>0.3424606232812744</v>
       </c>
       <c r="J23" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K23" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1744137301226798</v>
+        <v>0.1788689337054137</v>
       </c>
       <c r="M23" t="n">
-        <v>4.275146574889139</v>
+        <v>4.270358888547568</v>
       </c>
       <c r="N23" t="n">
-        <v>30.0268961973829</v>
+        <v>29.92698887325372</v>
       </c>
       <c r="O23" t="n">
-        <v>5.479680300654674</v>
+        <v>5.470556541454783</v>
       </c>
       <c r="P23" t="n">
-        <v>235.6688385437035</v>
+        <v>235.63440793059</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37766,28 +37948,28 @@
         <v>0.0614</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2090773255186429</v>
+        <v>0.2108704013276014</v>
       </c>
       <c r="J24" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K24" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0991236556129893</v>
+        <v>0.1017054349881983</v>
       </c>
       <c r="M24" t="n">
-        <v>3.750242359624379</v>
+        <v>3.742122726132643</v>
       </c>
       <c r="N24" t="n">
-        <v>21.92815452261429</v>
+        <v>21.83081910339589</v>
       </c>
       <c r="O24" t="n">
-        <v>4.682750743165206</v>
+        <v>4.67234620971048</v>
       </c>
       <c r="P24" t="n">
-        <v>268.7892365930845</v>
+        <v>268.771335545957</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37825,7 +38007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y389"/>
+  <dimension ref="A1:Y391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87195,6 +87377,260 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:54:22+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-38.60774311329714,178.18910187095355</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-38.60785469916487,178.18815703578358</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-38.60808570623274,178.18729563037866</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-38.60829534881295,178.18641930241532</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-38.608581768208026,178.1855966106222</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-38.60892084369262,178.18481070363927</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-38.609385335081186,178.18411240761972</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-38.60993911234381,178.1833408211308</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-38.610505497689644,178.1825730295034</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-38.61110696778169,178.1820133519029</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-38.611669177067355,178.181475239122</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-38.61220635755067,178.1808905083541</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-38.61274871078035,178.18031542215357</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-38.61343337866649,178.17989880831982</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>-38.614101715936734,178.17942047907027</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>-38.614747344892734,178.17900240027865</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>-38.61540820690944,178.17870097891188</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-38.61606059907516,178.17837093112723</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>-38.6166578743049,178.17780435571825</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>-38.61730482007184,178.17727697318162</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>-38.61795253661866,178.17674893672748</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>-38.6186598338611,178.17666120238883</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>-38.61939406090633,178.1767042493</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-38.60775217842377,178.18910820386483</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-38.60786147833624,178.18816177164862</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-38.60807719281851,178.1872896830578</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-38.60829968436661,178.1864223311202</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-38.60859438077664,178.1856054213515</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-38.608926913513244,178.18481494378503</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-38.60939463691104,178.18411890550323</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-38.60994647870248,178.18334815800787</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-38.61050912620133,178.18257886662334</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-38.61111361717982,178.18202573908238</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-38.61166953238064,178.18147590103632</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-38.61220813412801,178.1808938179437</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-38.61274967521389,178.18031721879785</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-38.61343641759236,178.17990570013976</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>-38.614102848911344,178.1794239734524</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>-38.61474525265005,178.1789953240082</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-38.61540918963307,178.17870430264472</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-38.61606113799064,178.17837275383545</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>-38.61665832631396,178.1778059749785</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>-38.61730685062046,178.17728564719388</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>-38.61795087022372,178.1767408463978</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>-38.61865828160706,178.17665366611485</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>-38.61939593272564,178.1767133372581</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0267/nzd0267.xlsx
+++ b/data/nzd0267/nzd0267.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y391"/>
+  <dimension ref="A1:Y393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32125,6 +32125,168 @@
         <v>276.39</v>
       </c>
       <c r="Y391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>298.05</v>
+      </c>
+      <c r="C392" t="n">
+        <v>273.65</v>
+      </c>
+      <c r="D392" t="n">
+        <v>257.97</v>
+      </c>
+      <c r="E392" t="n">
+        <v>252.57</v>
+      </c>
+      <c r="F392" t="n">
+        <v>247.39</v>
+      </c>
+      <c r="G392" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="H392" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="I392" t="n">
+        <v>292.45</v>
+      </c>
+      <c r="J392" t="n">
+        <v>289.7</v>
+      </c>
+      <c r="K392" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="L392" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="M392" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="N392" t="n">
+        <v>284.26</v>
+      </c>
+      <c r="O392" t="n">
+        <v>298.35</v>
+      </c>
+      <c r="P392" t="n">
+        <v>294.26</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="R392" t="n">
+        <v>293.86</v>
+      </c>
+      <c r="S392" t="n">
+        <v>294.89</v>
+      </c>
+      <c r="T392" t="n">
+        <v>274.87</v>
+      </c>
+      <c r="U392" t="n">
+        <v>256.66</v>
+      </c>
+      <c r="V392" t="n">
+        <v>228.44</v>
+      </c>
+      <c r="W392" t="n">
+        <v>244.97</v>
+      </c>
+      <c r="X392" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>294.97</v>
+      </c>
+      <c r="C393" t="n">
+        <v>274.79</v>
+      </c>
+      <c r="D393" t="n">
+        <v>263.14</v>
+      </c>
+      <c r="E393" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="F393" t="n">
+        <v>251.03</v>
+      </c>
+      <c r="G393" t="n">
+        <v>253.74</v>
+      </c>
+      <c r="H393" t="n">
+        <v>270.74</v>
+      </c>
+      <c r="I393" t="n">
+        <v>296.42</v>
+      </c>
+      <c r="J393" t="n">
+        <v>292.84</v>
+      </c>
+      <c r="K393" t="n">
+        <v>294.86</v>
+      </c>
+      <c r="L393" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="M393" t="n">
+        <v>289.66</v>
+      </c>
+      <c r="N393" t="n">
+        <v>285.61</v>
+      </c>
+      <c r="O393" t="n">
+        <v>299.65</v>
+      </c>
+      <c r="P393" t="n">
+        <v>296.18</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="R393" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="S393" t="n">
+        <v>295.08</v>
+      </c>
+      <c r="T393" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="U393" t="n">
+        <v>257.76</v>
+      </c>
+      <c r="V393" t="n">
+        <v>229.88</v>
+      </c>
+      <c r="W393" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="X393" t="n">
+        <v>278.61</v>
+      </c>
+      <c r="Y393" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32141,7 +32303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36064,6 +36226,26 @@
       </c>
       <c r="B392" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -36232,28 +36414,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7547812499603536</v>
+        <v>-0.7541465884550159</v>
       </c>
       <c r="J2" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K2" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2593971484102214</v>
+        <v>0.2614290545562455</v>
       </c>
       <c r="M2" t="n">
-        <v>7.281690312376682</v>
+        <v>7.25237834724658</v>
       </c>
       <c r="N2" t="n">
-        <v>90.19786725030393</v>
+        <v>89.75132582576548</v>
       </c>
       <c r="O2" t="n">
-        <v>9.497255774712183</v>
+        <v>9.473717634897373</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8948234149935</v>
+        <v>315.888442283401</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36310,28 +36492,28 @@
         <v>0.0786</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3224024072607645</v>
+        <v>-0.3153376200631925</v>
       </c>
       <c r="J3" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K3" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07261174526023673</v>
+        <v>0.07028979332712215</v>
       </c>
       <c r="M3" t="n">
-        <v>6.752358922348738</v>
+        <v>6.748183563346734</v>
       </c>
       <c r="N3" t="n">
-        <v>73.61819209456843</v>
+        <v>73.46794093293357</v>
       </c>
       <c r="O3" t="n">
-        <v>8.580104433779837</v>
+        <v>8.57134417305323</v>
       </c>
       <c r="P3" t="n">
-        <v>276.0749687594177</v>
+        <v>276.003767511636</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36388,28 +36570,28 @@
         <v>0.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02897020900221351</v>
+        <v>-0.02284013340672936</v>
       </c>
       <c r="J4" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K4" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003414414444867786</v>
+        <v>0.0002145835055752388</v>
       </c>
       <c r="M4" t="n">
-        <v>9.133593011285864</v>
+        <v>9.116685500974736</v>
       </c>
       <c r="N4" t="n">
-        <v>136.2613196038633</v>
+        <v>135.7683996062398</v>
       </c>
       <c r="O4" t="n">
-        <v>11.6731023984142</v>
+        <v>11.651969773658</v>
       </c>
       <c r="P4" t="n">
-        <v>255.533698063488</v>
+        <v>255.4718970146965</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36466,28 +36648,28 @@
         <v>0.0537</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006255600072617776</v>
+        <v>0.0186342215415543</v>
       </c>
       <c r="J5" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K5" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L5" t="n">
-        <v>1.993078490980515e-05</v>
+        <v>0.0001778271759684813</v>
       </c>
       <c r="M5" t="n">
-        <v>7.729718664045858</v>
+        <v>7.7391950531125</v>
       </c>
       <c r="N5" t="n">
-        <v>108.8776588944229</v>
+        <v>109.0531226373897</v>
       </c>
       <c r="O5" t="n">
-        <v>10.43444578760285</v>
+        <v>10.44285031193063</v>
       </c>
       <c r="P5" t="n">
-        <v>243.6702511843582</v>
+        <v>243.5454765358259</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36544,28 +36726,28 @@
         <v>0.1262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08692501064207292</v>
+        <v>0.09195089078604575</v>
       </c>
       <c r="J6" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K6" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065604073657678</v>
+        <v>0.01201556729864062</v>
       </c>
       <c r="M6" t="n">
-        <v>4.943967206817641</v>
+        <v>4.937906700137306</v>
       </c>
       <c r="N6" t="n">
-        <v>38.90225888128934</v>
+        <v>38.83369074122548</v>
       </c>
       <c r="O6" t="n">
-        <v>6.23716753673407</v>
+        <v>6.231668375421263</v>
       </c>
       <c r="P6" t="n">
-        <v>242.161236087472</v>
+        <v>242.1105700363608</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36622,28 +36804,28 @@
         <v>0.0742</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06944878626820485</v>
+        <v>-0.07003333686615433</v>
       </c>
       <c r="J7" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K7" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009349271179231344</v>
+        <v>0.009617668214361719</v>
       </c>
       <c r="M7" t="n">
-        <v>4.185729494803578</v>
+        <v>4.173067566144424</v>
       </c>
       <c r="N7" t="n">
-        <v>28.34040204850245</v>
+        <v>28.21198841737903</v>
       </c>
       <c r="O7" t="n">
-        <v>5.323570422987044</v>
+        <v>5.311495873798551</v>
       </c>
       <c r="P7" t="n">
-        <v>254.4380927338846</v>
+        <v>254.4439672227192</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36700,28 +36882,28 @@
         <v>0.0602</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08275214064200997</v>
+        <v>-0.08396894895755487</v>
       </c>
       <c r="J8" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K8" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008972104204664211</v>
+        <v>0.009346647188771096</v>
       </c>
       <c r="M8" t="n">
-        <v>5.044948432310064</v>
+        <v>5.025222091639757</v>
       </c>
       <c r="N8" t="n">
-        <v>41.94535984778406</v>
+        <v>41.74401934780099</v>
       </c>
       <c r="O8" t="n">
-        <v>6.476523747179814</v>
+        <v>6.460961178323314</v>
       </c>
       <c r="P8" t="n">
-        <v>272.9995572942521</v>
+        <v>273.0118092581807</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36778,28 +36960,28 @@
         <v>0.0639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.212295583212005</v>
+        <v>0.208271337421661</v>
       </c>
       <c r="J9" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K9" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04817923034589711</v>
+        <v>0.04692129767789199</v>
       </c>
       <c r="M9" t="n">
-        <v>5.522984013938537</v>
+        <v>5.512705546133029</v>
       </c>
       <c r="N9" t="n">
-        <v>49.37545573631365</v>
+        <v>49.21627341823135</v>
       </c>
       <c r="O9" t="n">
-        <v>7.026767089943543</v>
+        <v>7.015431092828961</v>
       </c>
       <c r="P9" t="n">
-        <v>292.62533498943</v>
+        <v>292.6658703820901</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36856,28 +37038,28 @@
         <v>0.066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2901377021539784</v>
+        <v>0.2838399074236766</v>
       </c>
       <c r="J10" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K10" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09494407667824711</v>
+        <v>0.09191129154670064</v>
       </c>
       <c r="M10" t="n">
-        <v>5.296921230806309</v>
+        <v>5.299214571326975</v>
       </c>
       <c r="N10" t="n">
-        <v>44.60464069822881</v>
+        <v>44.56747282121565</v>
       </c>
       <c r="O10" t="n">
-        <v>6.678670578657763</v>
+        <v>6.675887418255019</v>
       </c>
       <c r="P10" t="n">
-        <v>289.547082176594</v>
+        <v>289.6104816380228</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36934,28 +37116,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2963778705127635</v>
+        <v>0.2949894183370337</v>
       </c>
       <c r="J11" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K11" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1790214817219563</v>
+        <v>0.1793690979124338</v>
       </c>
       <c r="M11" t="n">
-        <v>3.659825838271762</v>
+        <v>3.647846098681694</v>
       </c>
       <c r="N11" t="n">
-        <v>22.33840049588155</v>
+        <v>22.23842790917433</v>
       </c>
       <c r="O11" t="n">
-        <v>4.726351710979786</v>
+        <v>4.715763767320658</v>
       </c>
       <c r="P11" t="n">
-        <v>287.2978133704005</v>
+        <v>287.311795687197</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37012,28 +37194,28 @@
         <v>0.0518</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2586327044627477</v>
+        <v>0.2598725759463799</v>
       </c>
       <c r="J12" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K12" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2265773615391833</v>
+        <v>0.2303273283136246</v>
       </c>
       <c r="M12" t="n">
-        <v>2.770920520698413</v>
+        <v>2.762266125596885</v>
       </c>
       <c r="N12" t="n">
-        <v>12.66196554138538</v>
+        <v>12.60585954238811</v>
       </c>
       <c r="O12" t="n">
-        <v>3.558365571633328</v>
+        <v>3.550473143453998</v>
       </c>
       <c r="P12" t="n">
-        <v>284.7449736248084</v>
+        <v>284.7324733353507</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37090,28 +37272,28 @@
         <v>0.0463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2765635967015257</v>
+        <v>0.2813445242581634</v>
       </c>
       <c r="J13" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K13" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2265984792188139</v>
+        <v>0.2335371882968068</v>
       </c>
       <c r="M13" t="n">
-        <v>2.852416672661714</v>
+        <v>2.858900876793733</v>
       </c>
       <c r="N13" t="n">
-        <v>14.47677885478623</v>
+        <v>14.51118702342438</v>
       </c>
       <c r="O13" t="n">
-        <v>3.804836245462639</v>
+        <v>3.809355197854931</v>
       </c>
       <c r="P13" t="n">
-        <v>276.7397267352391</v>
+        <v>276.6915363616261</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37168,28 +37350,28 @@
         <v>0.0502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2989322082728896</v>
+        <v>0.3077606980094891</v>
       </c>
       <c r="J14" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K14" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1583101696787657</v>
+        <v>0.166091855534915</v>
       </c>
       <c r="M14" t="n">
-        <v>4.06457549458163</v>
+        <v>4.087193347734776</v>
       </c>
       <c r="N14" t="n">
-        <v>26.34647797247764</v>
+        <v>26.56361392935063</v>
       </c>
       <c r="O14" t="n">
-        <v>5.132882033758192</v>
+        <v>5.153990097909641</v>
       </c>
       <c r="P14" t="n">
-        <v>268.6712979496057</v>
+        <v>268.582322024129</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37246,28 +37428,28 @@
         <v>0.0561</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1662503795323594</v>
+        <v>0.1685197396213299</v>
       </c>
       <c r="J15" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K15" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1129124876072238</v>
+        <v>0.1167134185585189</v>
       </c>
       <c r="M15" t="n">
-        <v>2.505686340219579</v>
+        <v>2.503306473510711</v>
       </c>
       <c r="N15" t="n">
-        <v>12.04158515397538</v>
+        <v>12.00530965776377</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4700987239523</v>
+        <v>3.464867913465645</v>
       </c>
       <c r="P15" t="n">
-        <v>292.4536364573439</v>
+        <v>292.4307606934038</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37324,28 +37506,28 @@
         <v>0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1215178708078947</v>
+        <v>0.1229935180761196</v>
       </c>
       <c r="J16" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K16" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06750634868283212</v>
+        <v>0.0697593041697655</v>
       </c>
       <c r="M16" t="n">
-        <v>2.450907805910064</v>
+        <v>2.445031171243047</v>
       </c>
       <c r="N16" t="n">
-        <v>11.31137624552005</v>
+        <v>11.26804591101575</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36323895159414</v>
+        <v>3.356791013902377</v>
       </c>
       <c r="P16" t="n">
-        <v>290.6080172543359</v>
+        <v>290.5931371499976</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37402,28 +37584,28 @@
         <v>0.0537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08926204098943429</v>
+        <v>0.09009309510547778</v>
       </c>
       <c r="J17" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K17" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0276290527765074</v>
+        <v>0.02843837277016203</v>
       </c>
       <c r="M17" t="n">
-        <v>2.881329012336432</v>
+        <v>2.87588254382193</v>
       </c>
       <c r="N17" t="n">
-        <v>15.55011067137002</v>
+        <v>15.4895781383614</v>
       </c>
       <c r="O17" t="n">
-        <v>3.943362863264046</v>
+        <v>3.9356801366932</v>
       </c>
       <c r="P17" t="n">
-        <v>285.5644345817005</v>
+        <v>285.5560426509921</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37480,28 +37662,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06380962243609109</v>
+        <v>0.06760252243057834</v>
       </c>
       <c r="J18" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K18" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01054043629429025</v>
+        <v>0.01192440804745276</v>
       </c>
       <c r="M18" t="n">
-        <v>3.044709891418046</v>
+        <v>3.046614585142358</v>
       </c>
       <c r="N18" t="n">
-        <v>21.20874354091325</v>
+        <v>21.1655078362019</v>
       </c>
       <c r="O18" t="n">
-        <v>4.605295163278164</v>
+        <v>4.600598638894932</v>
       </c>
       <c r="P18" t="n">
-        <v>288.9576718141894</v>
+        <v>288.9194191084245</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37558,28 +37740,28 @@
         <v>0.0365</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.08931358405519979</v>
+        <v>-0.08573977609945073</v>
       </c>
       <c r="J19" t="n">
+        <v>392</v>
+      </c>
+      <c r="K19" t="n">
         <v>390</v>
       </c>
-      <c r="K19" t="n">
-        <v>388</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01192378538317485</v>
+        <v>0.01111832384385236</v>
       </c>
       <c r="M19" t="n">
-        <v>3.91839374966982</v>
+        <v>3.9124630161835</v>
       </c>
       <c r="N19" t="n">
-        <v>36.09269467589971</v>
+        <v>35.96360391150326</v>
       </c>
       <c r="O19" t="n">
-        <v>6.007719590318752</v>
+        <v>5.996966225643034</v>
       </c>
       <c r="P19" t="n">
-        <v>294.0221147441077</v>
+        <v>293.9856746748032</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37636,28 +37818,28 @@
         <v>0.0659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1359630430900772</v>
+        <v>-0.1320361284974823</v>
       </c>
       <c r="J20" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K20" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1122141539305703</v>
+        <v>0.1068373395085984</v>
       </c>
       <c r="M20" t="n">
-        <v>2.220248401655631</v>
+        <v>2.227921573534732</v>
       </c>
       <c r="N20" t="n">
-        <v>8.129549904514747</v>
+        <v>8.16027408812381</v>
       </c>
       <c r="O20" t="n">
-        <v>2.851236557094964</v>
+        <v>2.856619346031916</v>
       </c>
       <c r="P20" t="n">
-        <v>275.5202255577926</v>
+        <v>275.4806767082173</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37714,28 +37896,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07211351490473358</v>
+        <v>-0.06092152529282829</v>
       </c>
       <c r="J21" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K21" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01601384659014826</v>
+        <v>0.01126700858889917</v>
       </c>
       <c r="M21" t="n">
-        <v>3.369538537899137</v>
+        <v>3.407865251777847</v>
       </c>
       <c r="N21" t="n">
-        <v>17.76195735440307</v>
+        <v>18.2357498214676</v>
       </c>
       <c r="O21" t="n">
-        <v>4.214493724565629</v>
+        <v>4.270333689709459</v>
       </c>
       <c r="P21" t="n">
-        <v>248.5326941880743</v>
+        <v>248.4199930119788</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37792,28 +37974,28 @@
         <v>0.1216</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2085009532655642</v>
+        <v>0.209709559076955</v>
       </c>
       <c r="J22" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K22" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08396256382517298</v>
+        <v>0.08579454091968119</v>
       </c>
       <c r="M22" t="n">
-        <v>3.962604160464777</v>
+        <v>3.949004936203162</v>
       </c>
       <c r="N22" t="n">
-        <v>26.36378688295678</v>
+        <v>26.23809490087963</v>
       </c>
       <c r="O22" t="n">
-        <v>5.134567837993455</v>
+        <v>5.122313432510708</v>
       </c>
       <c r="P22" t="n">
-        <v>222.4970372282931</v>
+        <v>222.4848604626238</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37870,28 +38052,28 @@
         <v>0.0709</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3424606232812744</v>
+        <v>0.3434467447613329</v>
       </c>
       <c r="J23" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K23" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1788689337054137</v>
+        <v>0.1815140736859903</v>
       </c>
       <c r="M23" t="n">
-        <v>4.270358888547568</v>
+        <v>4.253308922877198</v>
       </c>
       <c r="N23" t="n">
-        <v>29.92698887325372</v>
+        <v>29.78046057080153</v>
       </c>
       <c r="O23" t="n">
-        <v>5.470556541454783</v>
+        <v>5.457147658878356</v>
       </c>
       <c r="P23" t="n">
-        <v>235.63440793059</v>
+        <v>235.6244720122892</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37948,28 +38130,28 @@
         <v>0.0614</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2108704013276014</v>
+        <v>0.2144738697007484</v>
       </c>
       <c r="J24" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K24" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1017054349881983</v>
+        <v>0.1057410777833446</v>
       </c>
       <c r="M24" t="n">
-        <v>3.742122726132643</v>
+        <v>3.744927618862816</v>
       </c>
       <c r="N24" t="n">
-        <v>21.83081910339589</v>
+        <v>21.78111025085578</v>
       </c>
       <c r="O24" t="n">
-        <v>4.67234620971048</v>
+        <v>4.667023703695513</v>
       </c>
       <c r="P24" t="n">
-        <v>268.771335545957</v>
+        <v>268.7350428764969</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38007,7 +38189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y391"/>
+  <dimension ref="A1:Y393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87631,6 +87813,260 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-38.60774027551826,178.1890998884773</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-38.6078618724741,178.18816204698967</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-38.60805220436883,178.18727222657836</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-38.60832356932393,178.18643901653763</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-38.6085966668046,178.18560701829654</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-38.60893392927968,178.18481984473365</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-38.60939148374844,178.18411670283066</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-38.60994173306763,178.18334343136573</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-38.61050616756876,178.1825741071255</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-38.61111869305527,178.1820351949461</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-38.61167958266896,178.18149462375845</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-38.612219656498624,178.180915283</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-38.61276713653109,178.18034974752362</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-38.61344055757764,178.1799150889968</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-38.614106865820354,178.17943636262618</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-38.61474686938307,178.1790007920353</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-38.61541581508962,178.17872671103927</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-38.61606611503221,178.17838958708313</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>-38.616662334126595,178.17782033241986</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>-38.617307236167576,178.17728729415828</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>-38.61794306326978,178.1767029437616</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>-38.61865250630442,178.17662562674505</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>-38.61939714255966,178.17671921118244</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-38.6077159967416,178.18908292729853</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-38.60787085881712,178.18816832476577</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-38.6080929584001,178.18730069661612</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-38.608370314462086,178.1864716715305</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-38.608625360394484,178.18562706271916</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-38.60896065225264,178.18483851240117</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-38.60940858965492,178.18412865233182</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-38.609969852721434,178.18337143849337</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-38.61052369606796,178.1826023049108</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-38.611129149355946,178.18205467402942</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-38.61168531843805,178.1815053089506</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-38.61223062051233,178.18093570790558</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-38.6127739890801,178.18036251316147</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-38.613446283087804,178.17992807358803</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-38.61411345766797,178.17945669358076</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-38.61475802800349,178.17903853215017</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-38.61541816094395,178.17873464511285</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-38.61606671734916,178.1783916242279</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>-38.616666944615496,178.17783684887678</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>-38.61731006351242,178.1772993718977</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>-38.61794635040985,178.17671890276546</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>-38.61865554233396,178.17664036680856</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>-38.61940100033027,178.1767379412442</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0267/nzd0267.xlsx
+++ b/data/nzd0267/nzd0267.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y393"/>
+  <dimension ref="A1:Y395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32287,6 +32287,168 @@
         <v>278.61</v>
       </c>
       <c r="Y393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="C394" t="n">
+        <v>273.8</v>
+      </c>
+      <c r="D394" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="E394" t="n">
+        <v>259.91</v>
+      </c>
+      <c r="F394" t="n">
+        <v>253.79</v>
+      </c>
+      <c r="G394" t="n">
+        <v>254.53</v>
+      </c>
+      <c r="H394" t="n">
+        <v>270.59</v>
+      </c>
+      <c r="I394" t="n">
+        <v>296.03</v>
+      </c>
+      <c r="J394" t="n">
+        <v>292.97</v>
+      </c>
+      <c r="K394" t="n">
+        <v>294.98</v>
+      </c>
+      <c r="L394" t="n">
+        <v>293.09</v>
+      </c>
+      <c r="M394" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="N394" t="n">
+        <v>284.95</v>
+      </c>
+      <c r="O394" t="n">
+        <v>299.42</v>
+      </c>
+      <c r="P394" t="n">
+        <v>295.83</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="R394" t="n">
+        <v>294.89</v>
+      </c>
+      <c r="S394" t="n">
+        <v>294.54</v>
+      </c>
+      <c r="T394" t="n">
+        <v>276.56</v>
+      </c>
+      <c r="U394" t="n">
+        <v>257.11</v>
+      </c>
+      <c r="V394" t="n">
+        <v>229.87</v>
+      </c>
+      <c r="W394" t="n">
+        <v>246.32</v>
+      </c>
+      <c r="X394" t="n">
+        <v>278.06</v>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>294.93</v>
+      </c>
+      <c r="C395" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="D395" t="n">
+        <v>263.86</v>
+      </c>
+      <c r="E395" t="n">
+        <v>258.98</v>
+      </c>
+      <c r="F395" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="G395" t="n">
+        <v>255.52</v>
+      </c>
+      <c r="H395" t="n">
+        <v>270.82</v>
+      </c>
+      <c r="I395" t="n">
+        <v>295.96</v>
+      </c>
+      <c r="J395" t="n">
+        <v>293.38</v>
+      </c>
+      <c r="K395" t="n">
+        <v>294.88</v>
+      </c>
+      <c r="L395" t="n">
+        <v>293.32</v>
+      </c>
+      <c r="M395" t="n">
+        <v>288.54</v>
+      </c>
+      <c r="N395" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="O395" t="n">
+        <v>299.29</v>
+      </c>
+      <c r="P395" t="n">
+        <v>296.24</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>290.83</v>
+      </c>
+      <c r="R395" t="n">
+        <v>294.11</v>
+      </c>
+      <c r="S395" t="n">
+        <v>294.46</v>
+      </c>
+      <c r="T395" t="n">
+        <v>276.35</v>
+      </c>
+      <c r="U395" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="V395" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="W395" t="n">
+        <v>246.64</v>
+      </c>
+      <c r="X395" t="n">
+        <v>277.78</v>
+      </c>
+      <c r="Y395" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32303,7 +32465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36246,6 +36408,26 @@
       </c>
       <c r="B394" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -36414,28 +36596,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7541465884550159</v>
+        <v>-0.7544238283790496</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2614290545562455</v>
+        <v>0.2639331363770651</v>
       </c>
       <c r="M2" t="n">
-        <v>7.25237834724658</v>
+        <v>7.218956462187217</v>
       </c>
       <c r="N2" t="n">
-        <v>89.75132582576548</v>
+        <v>89.29839040147317</v>
       </c>
       <c r="O2" t="n">
-        <v>9.473717634897373</v>
+        <v>9.449782558422875</v>
       </c>
       <c r="P2" t="n">
-        <v>315.888442283401</v>
+        <v>315.8912457118797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36492,28 +36674,28 @@
         <v>0.0786</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3153376200631925</v>
+        <v>-0.3097371564888685</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07028979332712215</v>
+        <v>0.06863374483923446</v>
       </c>
       <c r="M3" t="n">
-        <v>6.748183563346734</v>
+        <v>6.738407156571489</v>
       </c>
       <c r="N3" t="n">
-        <v>73.46794093293357</v>
+        <v>73.24178249467441</v>
       </c>
       <c r="O3" t="n">
-        <v>8.57134417305323</v>
+        <v>8.558141299059885</v>
       </c>
       <c r="P3" t="n">
-        <v>276.003767511636</v>
+        <v>275.9472052911524</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36570,28 +36752,28 @@
         <v>0.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02284013340672936</v>
+        <v>-0.01227636107644657</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002145835055752388</v>
+        <v>6.252508983406457e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>9.116685500974736</v>
+        <v>9.121399473069832</v>
       </c>
       <c r="N4" t="n">
-        <v>135.7683996062398</v>
+        <v>135.5961366083369</v>
       </c>
       <c r="O4" t="n">
-        <v>11.651969773658</v>
+        <v>11.64457541554594</v>
       </c>
       <c r="P4" t="n">
-        <v>255.4718970146965</v>
+        <v>255.3652056668043</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36648,28 +36830,28 @@
         <v>0.0537</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0186342215415543</v>
+        <v>0.03472235494377059</v>
       </c>
       <c r="J5" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K5" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001778271759684813</v>
+        <v>0.000618006942715299</v>
       </c>
       <c r="M5" t="n">
-        <v>7.7391950531125</v>
+        <v>7.76698961755795</v>
       </c>
       <c r="N5" t="n">
-        <v>109.0531226373897</v>
+        <v>109.6846866347632</v>
       </c>
       <c r="O5" t="n">
-        <v>10.44285031193063</v>
+        <v>10.47304571911931</v>
       </c>
       <c r="P5" t="n">
-        <v>243.5454765358259</v>
+        <v>243.3829846325988</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36726,28 +36908,28 @@
         <v>0.1262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09195089078604575</v>
+        <v>0.1017631345315404</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K6" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01201556729864062</v>
+        <v>0.01468997591164189</v>
       </c>
       <c r="M6" t="n">
-        <v>4.937906700137306</v>
+        <v>4.951519777471924</v>
       </c>
       <c r="N6" t="n">
-        <v>38.83369074122548</v>
+        <v>39.07709378735902</v>
       </c>
       <c r="O6" t="n">
-        <v>6.231668375421263</v>
+        <v>6.251167393964028</v>
       </c>
       <c r="P6" t="n">
-        <v>242.1105700363608</v>
+        <v>242.0114632010201</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36804,28 +36986,28 @@
         <v>0.0742</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07003333686615433</v>
+        <v>-0.06748436725773534</v>
       </c>
       <c r="J7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009617668214361719</v>
+        <v>0.009035484647637038</v>
       </c>
       <c r="M7" t="n">
-        <v>4.173067566144424</v>
+        <v>4.163825160557041</v>
       </c>
       <c r="N7" t="n">
-        <v>28.21198841737903</v>
+        <v>28.09975283418101</v>
       </c>
       <c r="O7" t="n">
-        <v>5.311495873798551</v>
+        <v>5.300919998847466</v>
       </c>
       <c r="P7" t="n">
-        <v>254.4439672227192</v>
+        <v>254.4182196025849</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36882,28 +37064,28 @@
         <v>0.0602</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08396894895755487</v>
+        <v>-0.08405030140524207</v>
       </c>
       <c r="J8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009346647188771096</v>
+        <v>0.009478656177348221</v>
       </c>
       <c r="M8" t="n">
-        <v>5.025222091639757</v>
+        <v>5.000297066523198</v>
       </c>
       <c r="N8" t="n">
-        <v>41.74401934780099</v>
+        <v>41.53221623868053</v>
       </c>
       <c r="O8" t="n">
-        <v>6.460961178323314</v>
+        <v>6.444549343335074</v>
       </c>
       <c r="P8" t="n">
-        <v>273.0118092581807</v>
+        <v>273.0126303940967</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36960,28 +37142,28 @@
         <v>0.0639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.208271337421661</v>
+        <v>0.2059791346653809</v>
       </c>
       <c r="J9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04692129767789199</v>
+        <v>0.04645835959638578</v>
       </c>
       <c r="M9" t="n">
-        <v>5.512705546133029</v>
+        <v>5.494831740415831</v>
       </c>
       <c r="N9" t="n">
-        <v>49.21627341823135</v>
+        <v>48.99048498025618</v>
       </c>
       <c r="O9" t="n">
-        <v>7.015431092828961</v>
+        <v>6.999320322735358</v>
       </c>
       <c r="P9" t="n">
-        <v>292.6658703820901</v>
+        <v>292.6890223694995</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37038,28 +37220,28 @@
         <v>0.066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2838399074236766</v>
+        <v>0.2797018188789985</v>
       </c>
       <c r="J10" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K10" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09191129154670064</v>
+        <v>0.09034322643463011</v>
       </c>
       <c r="M10" t="n">
-        <v>5.299214571326975</v>
+        <v>5.291484217241941</v>
       </c>
       <c r="N10" t="n">
-        <v>44.56747282121565</v>
+        <v>44.41945524821724</v>
       </c>
       <c r="O10" t="n">
-        <v>6.675887418255019</v>
+        <v>6.664792213431507</v>
       </c>
       <c r="P10" t="n">
-        <v>289.6104816380228</v>
+        <v>289.6522427152539</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37116,28 +37298,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2949894183370337</v>
+        <v>0.2947709614010985</v>
       </c>
       <c r="J11" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K11" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1793690979124338</v>
+        <v>0.1809541858878042</v>
       </c>
       <c r="M11" t="n">
-        <v>3.647846098681694</v>
+        <v>3.630369823860014</v>
       </c>
       <c r="N11" t="n">
-        <v>22.23842790917433</v>
+        <v>22.12577264016115</v>
       </c>
       <c r="O11" t="n">
-        <v>4.715763767320658</v>
+        <v>4.703804060562168</v>
       </c>
       <c r="P11" t="n">
-        <v>287.311795687197</v>
+        <v>287.3140023893123</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37194,28 +37376,28 @@
         <v>0.0518</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2598725759463799</v>
+        <v>0.2615220705104067</v>
       </c>
       <c r="J12" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K12" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2303273283136246</v>
+        <v>0.2345881720659866</v>
       </c>
       <c r="M12" t="n">
-        <v>2.762266125596885</v>
+        <v>2.755706405534586</v>
       </c>
       <c r="N12" t="n">
-        <v>12.60585954238811</v>
+        <v>12.5543790803855</v>
       </c>
       <c r="O12" t="n">
-        <v>3.550473143453998</v>
+        <v>3.543215923477639</v>
       </c>
       <c r="P12" t="n">
-        <v>284.7324733353507</v>
+        <v>284.7158124913746</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37272,28 +37454,28 @@
         <v>0.0463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2813445242581634</v>
+        <v>0.28598246949724</v>
       </c>
       <c r="J13" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K13" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2335371882968068</v>
+        <v>0.2404317876854817</v>
       </c>
       <c r="M13" t="n">
-        <v>2.858900876793733</v>
+        <v>2.865222827481155</v>
       </c>
       <c r="N13" t="n">
-        <v>14.51118702342438</v>
+        <v>14.53594289314305</v>
       </c>
       <c r="O13" t="n">
-        <v>3.809355197854931</v>
+        <v>3.812603164918039</v>
       </c>
       <c r="P13" t="n">
-        <v>276.6915363616261</v>
+        <v>276.6446922463144</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37350,28 +37532,28 @@
         <v>0.0502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3077606980094891</v>
+        <v>0.3160386807062431</v>
       </c>
       <c r="J14" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K14" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L14" t="n">
-        <v>0.166091855534915</v>
+        <v>0.1736350531020139</v>
       </c>
       <c r="M14" t="n">
-        <v>4.087193347734776</v>
+        <v>4.107912653849818</v>
       </c>
       <c r="N14" t="n">
-        <v>26.56361392935063</v>
+        <v>26.7426506625486</v>
       </c>
       <c r="O14" t="n">
-        <v>5.153990097909641</v>
+        <v>5.171329680319038</v>
       </c>
       <c r="P14" t="n">
-        <v>268.582322024129</v>
+        <v>268.4987136943475</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37428,28 +37610,28 @@
         <v>0.0561</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1685197396213299</v>
+        <v>0.1710799003176196</v>
       </c>
       <c r="J15" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K15" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1167134185585189</v>
+        <v>0.1208869184470629</v>
       </c>
       <c r="M15" t="n">
-        <v>2.503306473510711</v>
+        <v>2.502509008643064</v>
       </c>
       <c r="N15" t="n">
-        <v>12.00530965776377</v>
+        <v>11.97437627076796</v>
       </c>
       <c r="O15" t="n">
-        <v>3.464867913465645</v>
+        <v>3.460401171940612</v>
       </c>
       <c r="P15" t="n">
-        <v>292.4307606934038</v>
+        <v>292.4049027624421</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37506,28 +37688,28 @@
         <v>0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1229935180761196</v>
+        <v>0.1252688525510919</v>
       </c>
       <c r="J16" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K16" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0697593041697655</v>
+        <v>0.07285512671112371</v>
       </c>
       <c r="M16" t="n">
-        <v>2.445031171243047</v>
+        <v>2.442763802618148</v>
       </c>
       <c r="N16" t="n">
-        <v>11.26804591101575</v>
+        <v>11.23474372680561</v>
       </c>
       <c r="O16" t="n">
-        <v>3.356791013902377</v>
+        <v>3.351826923754509</v>
       </c>
       <c r="P16" t="n">
-        <v>290.5931371499976</v>
+        <v>290.5701547127841</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37584,28 +37766,28 @@
         <v>0.0537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09009309510547778</v>
+        <v>0.09287552625634306</v>
       </c>
       <c r="J17" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K17" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02843837277016203</v>
+        <v>0.03045967357419788</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87588254382193</v>
+        <v>2.875554424702778</v>
       </c>
       <c r="N17" t="n">
-        <v>15.4895781383614</v>
+        <v>15.44659273723084</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9356801366932</v>
+        <v>3.930215355070361</v>
       </c>
       <c r="P17" t="n">
-        <v>285.5560426509921</v>
+        <v>285.5279383786003</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37662,28 +37844,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06760252243057834</v>
+        <v>0.0715598704800412</v>
       </c>
       <c r="J18" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K18" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01192440804745276</v>
+        <v>0.01345816646287978</v>
       </c>
       <c r="M18" t="n">
-        <v>3.046614585142358</v>
+        <v>3.049544807400077</v>
       </c>
       <c r="N18" t="n">
-        <v>21.1655078362019</v>
+        <v>21.13032747947351</v>
       </c>
       <c r="O18" t="n">
-        <v>4.600598638894932</v>
+        <v>4.596773594541449</v>
       </c>
       <c r="P18" t="n">
-        <v>288.9194191084245</v>
+        <v>288.8794233073241</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37740,28 +37922,28 @@
         <v>0.0365</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.08573977609945073</v>
+        <v>-0.08278272700715089</v>
       </c>
       <c r="J19" t="n">
+        <v>394</v>
+      </c>
+      <c r="K19" t="n">
         <v>392</v>
       </c>
-      <c r="K19" t="n">
-        <v>390</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01111832384385236</v>
+        <v>0.01048826974067274</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9124630161835</v>
+        <v>3.904095609771004</v>
       </c>
       <c r="N19" t="n">
-        <v>35.96360391150326</v>
+        <v>35.81922591849538</v>
       </c>
       <c r="O19" t="n">
-        <v>5.996966225643034</v>
+        <v>5.984916533962306</v>
       </c>
       <c r="P19" t="n">
-        <v>293.9856746748032</v>
+        <v>293.9554573241293</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37818,28 +38000,28 @@
         <v>0.0659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1320361284974823</v>
+        <v>-0.1273570917835383</v>
       </c>
       <c r="J20" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K20" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1068373395085984</v>
+        <v>0.1001361635756413</v>
       </c>
       <c r="M20" t="n">
-        <v>2.227921573534732</v>
+        <v>2.239551921653563</v>
       </c>
       <c r="N20" t="n">
-        <v>8.16027408812381</v>
+        <v>8.219261587374529</v>
       </c>
       <c r="O20" t="n">
-        <v>2.856619346031916</v>
+        <v>2.866925458984682</v>
       </c>
       <c r="P20" t="n">
-        <v>275.4806767082173</v>
+        <v>275.4334558440759</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37896,28 +38078,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06092152529282829</v>
+        <v>-0.05053068604708295</v>
       </c>
       <c r="J21" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K21" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01126700858889917</v>
+        <v>0.007665594734241554</v>
       </c>
       <c r="M21" t="n">
-        <v>3.407865251777847</v>
+        <v>3.443505847908368</v>
       </c>
       <c r="N21" t="n">
-        <v>18.2357498214676</v>
+        <v>18.63902834967866</v>
       </c>
       <c r="O21" t="n">
-        <v>4.270333689709459</v>
+        <v>4.317294100438221</v>
       </c>
       <c r="P21" t="n">
-        <v>248.4199930119788</v>
+        <v>248.3151291970838</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37974,28 +38156,28 @@
         <v>0.1216</v>
       </c>
       <c r="I22" t="n">
-        <v>0.209709559076955</v>
+        <v>0.2118873848907697</v>
       </c>
       <c r="J22" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K22" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08579454091968119</v>
+        <v>0.08834044797599994</v>
       </c>
       <c r="M22" t="n">
-        <v>3.949004936203162</v>
+        <v>3.940822093814128</v>
       </c>
       <c r="N22" t="n">
-        <v>26.23809490087963</v>
+        <v>26.1266650245842</v>
       </c>
       <c r="O22" t="n">
-        <v>5.122313432510708</v>
+        <v>5.111424950499048</v>
       </c>
       <c r="P22" t="n">
-        <v>222.4848604626238</v>
+        <v>222.4628803535529</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38052,28 +38234,28 @@
         <v>0.0709</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3434467447613329</v>
+        <v>0.3452677793864077</v>
       </c>
       <c r="J23" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K23" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1815140736859903</v>
+        <v>0.1848466769859219</v>
       </c>
       <c r="M23" t="n">
-        <v>4.253308922877198</v>
+        <v>4.240438433174731</v>
       </c>
       <c r="N23" t="n">
-        <v>29.78046057080153</v>
+        <v>29.6442484640832</v>
       </c>
       <c r="O23" t="n">
-        <v>5.457147658878356</v>
+        <v>5.444653199615491</v>
       </c>
       <c r="P23" t="n">
-        <v>235.6244720122892</v>
+        <v>235.6060931579813</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38130,28 +38312,28 @@
         <v>0.0614</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2144738697007484</v>
+        <v>0.2181198416922118</v>
       </c>
       <c r="J24" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K24" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1057410777833446</v>
+        <v>0.1098876377615922</v>
       </c>
       <c r="M24" t="n">
-        <v>3.744927618862816</v>
+        <v>3.748001190329892</v>
       </c>
       <c r="N24" t="n">
-        <v>21.78111025085578</v>
+        <v>21.73136611723466</v>
       </c>
       <c r="O24" t="n">
-        <v>4.667023703695513</v>
+        <v>4.661691336546711</v>
       </c>
       <c r="P24" t="n">
-        <v>268.7350428764969</v>
+        <v>268.6982479985712</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38189,7 +38371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y393"/>
+  <dimension ref="A1:Y395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88067,6 +88249,260 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-38.60772640193199,178.18909019637366</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-38.60786305488769,178.18816287301274</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-38.608116291458266,178.18731699669186</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-38.60838142924017,178.1864794360464</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-38.60864711706941,178.18564226124872</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-38.608966879729536,178.1848428626857</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-38.609407407219045,178.18412782632925</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-38.609967090337676,178.18336868716244</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-38.61052442176998,178.18260347233533</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-38.611129758460734,178.18205580873348</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-38.611684100221694,178.1815030395291</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-38.61222549382124,178.18092615737027</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-38.61277063894523,178.18035627218268</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-38.61344527011304,178.1799257763141</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-38.61411225602937,178.1794529874169</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-38.61475780609921,178.17903778163642</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-38.615419080265085,178.1787377544121</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-38.61606500550088,178.17838583444814</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>-38.616667426757985,178.17783857608808</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>-38.61730839280882,178.17729223505157</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>-38.61794632758251,178.17671879193904</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>-38.61865558798852,178.17664058846364</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>-38.61939974484314,178.1767318456618</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-38.60771568143278,178.18908270702354</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-38.607850442475744,178.18815406210138</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-38.60809863400913,178.1873046614984</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-38.60837409821641,178.18647431476967</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-38.60864956075376,178.18564396833057</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-38.608974683782556,178.1848483143092</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-38.60940922028739,178.18412909286653</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-38.60996659452519,178.18336819333385</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-38.61052671052246,178.18260715421283</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-38.61112925087342,178.18205486314676</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-38.61168526767905,178.18150521439136</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-38.612224935468696,178.18092511721304</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-38.61276784716587,178.18035107136745</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-38.61344469756207,178.17992447785488</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>-38.614113663663154,178.17945732892315</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-38.61475916922529,178.17904239193524</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-38.61541660760803,178.1787293914695</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-38.61606475189369,178.178384976703</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>-38.61666679394597,178.17783630912325</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>-38.61730656788588,178.17728443942</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>-38.6179475374321,178.17672466573939</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>-38.618656318461504,178.17664413494524</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>-38.61939910568593,178.17672874245628</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0267/nzd0267.xlsx
+++ b/data/nzd0267/nzd0267.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y395"/>
+  <dimension ref="A1:Y398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32449,6 +32449,249 @@
         <v>277.78</v>
       </c>
       <c r="Y395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>295.12</v>
+      </c>
+      <c r="C396" t="n">
+        <v>271.92</v>
+      </c>
+      <c r="D396" t="n">
+        <v>264.77</v>
+      </c>
+      <c r="E396" t="n">
+        <v>259.53</v>
+      </c>
+      <c r="F396" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="G396" t="n">
+        <v>256.03</v>
+      </c>
+      <c r="H396" t="n">
+        <v>271.34</v>
+      </c>
+      <c r="I396" t="n">
+        <v>295.61</v>
+      </c>
+      <c r="J396" t="n">
+        <v>293.49</v>
+      </c>
+      <c r="K396" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="L396" t="n">
+        <v>293.42</v>
+      </c>
+      <c r="M396" t="n">
+        <v>287.96</v>
+      </c>
+      <c r="N396" t="n">
+        <v>283.71</v>
+      </c>
+      <c r="O396" t="n">
+        <v>299.01</v>
+      </c>
+      <c r="P396" t="n">
+        <v>295.86</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>290.87</v>
+      </c>
+      <c r="R396" t="n">
+        <v>293.52</v>
+      </c>
+      <c r="S396" t="n">
+        <v>294.11</v>
+      </c>
+      <c r="T396" t="n">
+        <v>275.88</v>
+      </c>
+      <c r="U396" t="n">
+        <v>256.32</v>
+      </c>
+      <c r="V396" t="n">
+        <v>230.45</v>
+      </c>
+      <c r="W396" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="X396" t="n">
+        <v>277.68</v>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="C397" t="n">
+        <v>270.54</v>
+      </c>
+      <c r="D397" t="n">
+        <v>262.96</v>
+      </c>
+      <c r="E397" t="n">
+        <v>259.02</v>
+      </c>
+      <c r="F397" t="n">
+        <v>254.83</v>
+      </c>
+      <c r="G397" t="n">
+        <v>256.89</v>
+      </c>
+      <c r="H397" t="n">
+        <v>272.46</v>
+      </c>
+      <c r="I397" t="n">
+        <v>295.69</v>
+      </c>
+      <c r="J397" t="n">
+        <v>293.88</v>
+      </c>
+      <c r="K397" t="n">
+        <v>294.29</v>
+      </c>
+      <c r="L397" t="n">
+        <v>292.56</v>
+      </c>
+      <c r="M397" t="n">
+        <v>286.91</v>
+      </c>
+      <c r="N397" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="O397" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="P397" t="n">
+        <v>294.55</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="R397" t="n">
+        <v>292.12</v>
+      </c>
+      <c r="S397" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="T397" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="U397" t="n">
+        <v>253.91</v>
+      </c>
+      <c r="V397" t="n">
+        <v>229.72</v>
+      </c>
+      <c r="W397" t="n">
+        <v>246.32</v>
+      </c>
+      <c r="X397" t="n">
+        <v>276.89</v>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>293.59</v>
+      </c>
+      <c r="C398" t="n">
+        <v>269.73</v>
+      </c>
+      <c r="D398" t="n">
+        <v>261.73</v>
+      </c>
+      <c r="E398" t="n">
+        <v>257.75</v>
+      </c>
+      <c r="F398" t="n">
+        <v>254.63</v>
+      </c>
+      <c r="G398" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="H398" t="n">
+        <v>273.45</v>
+      </c>
+      <c r="I398" t="n">
+        <v>295.74</v>
+      </c>
+      <c r="J398" t="n">
+        <v>295</v>
+      </c>
+      <c r="K398" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="L398" t="n">
+        <v>293.09</v>
+      </c>
+      <c r="M398" t="n">
+        <v>286.51</v>
+      </c>
+      <c r="N398" t="n">
+        <v>281.21</v>
+      </c>
+      <c r="O398" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="P398" t="n">
+        <v>294.54</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>290.71</v>
+      </c>
+      <c r="R398" t="n">
+        <v>292.56</v>
+      </c>
+      <c r="S398" t="n">
+        <v>294.09</v>
+      </c>
+      <c r="T398" t="n">
+        <v>275.44</v>
+      </c>
+      <c r="U398" t="n">
+        <v>253.25</v>
+      </c>
+      <c r="V398" t="n">
+        <v>230.44</v>
+      </c>
+      <c r="W398" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="X398" t="n">
+        <v>278.29</v>
+      </c>
+      <c r="Y398" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32465,7 +32708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36428,6 +36671,36 @@
       </c>
       <c r="B396" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -36596,28 +36869,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7544238283790496</v>
+        <v>-0.7565274230157756</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2639331363770651</v>
+        <v>0.2685188394787017</v>
       </c>
       <c r="M2" t="n">
-        <v>7.218956462187217</v>
+        <v>7.174292263369538</v>
       </c>
       <c r="N2" t="n">
-        <v>89.29839040147317</v>
+        <v>88.64009213645747</v>
       </c>
       <c r="O2" t="n">
-        <v>9.449782558422875</v>
+        <v>9.414886729879306</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8912457118797</v>
+        <v>315.9125838890025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36674,28 +36947,28 @@
         <v>0.0786</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3097371564888685</v>
+        <v>-0.305085996497759</v>
       </c>
       <c r="J3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06863374483923446</v>
+        <v>0.0677960315990549</v>
       </c>
       <c r="M3" t="n">
-        <v>6.738407156571489</v>
+        <v>6.707908348248571</v>
       </c>
       <c r="N3" t="n">
-        <v>73.24178249467441</v>
+        <v>72.76184226594924</v>
       </c>
       <c r="O3" t="n">
-        <v>8.558141299059885</v>
+        <v>8.530055232291831</v>
       </c>
       <c r="P3" t="n">
-        <v>275.9472052911524</v>
+        <v>275.9000898913751</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36752,28 +37025,28 @@
         <v>0.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01227636107644657</v>
+        <v>0.0001940872833640292</v>
       </c>
       <c r="J4" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K4" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L4" t="n">
-        <v>6.252508983406457e-05</v>
+        <v>1.585600073461535e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>9.121399473069832</v>
+        <v>9.111857784907963</v>
       </c>
       <c r="N4" t="n">
-        <v>135.5961366083369</v>
+        <v>135.0681536359053</v>
       </c>
       <c r="O4" t="n">
-        <v>11.64457541554594</v>
+        <v>11.62188253407791</v>
       </c>
       <c r="P4" t="n">
-        <v>255.3652056668043</v>
+        <v>255.2388503637356</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36830,28 +37103,28 @@
         <v>0.0537</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03472235494377059</v>
+        <v>0.05695696124456526</v>
       </c>
       <c r="J5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000618006942715299</v>
+        <v>0.001667826643789727</v>
       </c>
       <c r="M5" t="n">
-        <v>7.76698961755795</v>
+        <v>7.807159259342547</v>
       </c>
       <c r="N5" t="n">
-        <v>109.6846866347632</v>
+        <v>110.4002981740459</v>
       </c>
       <c r="O5" t="n">
-        <v>10.47304571911931</v>
+        <v>10.50715461835629</v>
       </c>
       <c r="P5" t="n">
-        <v>243.3829846325988</v>
+        <v>243.157653242266</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36908,28 +37181,28 @@
         <v>0.1262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1017631345315404</v>
+        <v>0.116844188983005</v>
       </c>
       <c r="J6" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K6" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01468997591164189</v>
+        <v>0.0192761047842479</v>
       </c>
       <c r="M6" t="n">
-        <v>4.951519777471924</v>
+        <v>4.975278409335526</v>
       </c>
       <c r="N6" t="n">
-        <v>39.07709378735902</v>
+        <v>39.49064073288317</v>
       </c>
       <c r="O6" t="n">
-        <v>6.251167393964028</v>
+        <v>6.284157917564069</v>
       </c>
       <c r="P6" t="n">
-        <v>242.0114632010201</v>
+        <v>241.858607742594</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36986,28 +37259,28 @@
         <v>0.0742</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06748436725773534</v>
+        <v>-0.06114908757414014</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009035484647637038</v>
+        <v>0.007531267942560094</v>
       </c>
       <c r="M7" t="n">
-        <v>4.163825160557041</v>
+        <v>4.162404171122786</v>
       </c>
       <c r="N7" t="n">
-        <v>28.09975283418101</v>
+        <v>28.01438941230454</v>
       </c>
       <c r="O7" t="n">
-        <v>5.300919998847466</v>
+        <v>5.292862119147309</v>
       </c>
       <c r="P7" t="n">
-        <v>254.4182196025849</v>
+        <v>254.3539952198393</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37064,28 +37337,28 @@
         <v>0.0602</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08405030140524207</v>
+        <v>-0.08152371483313328</v>
       </c>
       <c r="J8" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009478656177348221</v>
+        <v>0.00907821606541348</v>
       </c>
       <c r="M8" t="n">
-        <v>5.000297066523198</v>
+        <v>4.974338287641347</v>
       </c>
       <c r="N8" t="n">
-        <v>41.53221623868053</v>
+        <v>41.24385467861197</v>
       </c>
       <c r="O8" t="n">
-        <v>6.444549343335074</v>
+        <v>6.422137858891849</v>
       </c>
       <c r="P8" t="n">
-        <v>273.0126303940967</v>
+        <v>272.9869975826707</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37142,28 +37415,28 @@
         <v>0.0639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2059791346653809</v>
+        <v>0.202147909045051</v>
       </c>
       <c r="J9" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04645835959638578</v>
+        <v>0.04556301620520586</v>
       </c>
       <c r="M9" t="n">
-        <v>5.494831740415831</v>
+        <v>5.469953013930036</v>
       </c>
       <c r="N9" t="n">
-        <v>48.99048498025618</v>
+        <v>48.66601271798037</v>
       </c>
       <c r="O9" t="n">
-        <v>6.999320322735358</v>
+        <v>6.976102975012652</v>
       </c>
       <c r="P9" t="n">
-        <v>292.6890223694995</v>
+        <v>292.727851514536</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37220,28 +37493,28 @@
         <v>0.066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2797018188789985</v>
+        <v>0.2751339765749656</v>
       </c>
       <c r="J10" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K10" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09034322643463011</v>
+        <v>0.08900437307851039</v>
       </c>
       <c r="M10" t="n">
-        <v>5.291484217241941</v>
+        <v>5.273032640710325</v>
       </c>
       <c r="N10" t="n">
-        <v>44.41945524821724</v>
+        <v>44.15123365720216</v>
       </c>
       <c r="O10" t="n">
-        <v>6.664792213431507</v>
+        <v>6.644639467811791</v>
       </c>
       <c r="P10" t="n">
-        <v>289.6522427152539</v>
+        <v>289.6984839856053</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37298,28 +37571,28 @@
         <v>0.0696</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2947709614010985</v>
+        <v>0.294084817814692</v>
       </c>
       <c r="J11" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1809541858878042</v>
+        <v>0.1829384594481552</v>
       </c>
       <c r="M11" t="n">
-        <v>3.630369823860014</v>
+        <v>3.606191252636048</v>
       </c>
       <c r="N11" t="n">
-        <v>22.12577264016115</v>
+        <v>21.96076298905773</v>
       </c>
       <c r="O11" t="n">
-        <v>4.703804060562168</v>
+        <v>4.686231213785523</v>
       </c>
       <c r="P11" t="n">
-        <v>287.3140023893123</v>
+        <v>287.320953078025</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37376,28 +37649,28 @@
         <v>0.0518</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2615220705104067</v>
+        <v>0.2635890824188301</v>
       </c>
       <c r="J12" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K12" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2345881720659866</v>
+        <v>0.2405089279827134</v>
       </c>
       <c r="M12" t="n">
-        <v>2.755706405534586</v>
+        <v>2.744197367441283</v>
       </c>
       <c r="N12" t="n">
-        <v>12.5543790803855</v>
+        <v>12.47379986392929</v>
       </c>
       <c r="O12" t="n">
-        <v>3.543215923477639</v>
+        <v>3.531826703552893</v>
       </c>
       <c r="P12" t="n">
-        <v>284.7158124913746</v>
+        <v>284.6948660088303</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37454,28 +37727,28 @@
         <v>0.0463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.28598246949724</v>
+        <v>0.2903953862665818</v>
       </c>
       <c r="J13" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K13" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2404317876854817</v>
+        <v>0.2486170204244507</v>
       </c>
       <c r="M13" t="n">
-        <v>2.865222827481155</v>
+        <v>2.863692086279375</v>
       </c>
       <c r="N13" t="n">
-        <v>14.53594289314305</v>
+        <v>14.48979979181085</v>
       </c>
       <c r="O13" t="n">
-        <v>3.812603164918039</v>
+        <v>3.806546964351137</v>
       </c>
       <c r="P13" t="n">
-        <v>276.6446922463144</v>
+        <v>276.5999834536782</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37532,28 +37805,28 @@
         <v>0.0502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3160386807062431</v>
+        <v>0.3242563067134923</v>
       </c>
       <c r="J14" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K14" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1736350531020139</v>
+        <v>0.1825927009416864</v>
       </c>
       <c r="M14" t="n">
-        <v>4.107912653849818</v>
+        <v>4.118750497457381</v>
       </c>
       <c r="N14" t="n">
-        <v>26.7426506625486</v>
+        <v>26.75989634610613</v>
       </c>
       <c r="O14" t="n">
-        <v>5.171329680319038</v>
+        <v>5.172996843813665</v>
       </c>
       <c r="P14" t="n">
-        <v>268.4987136943475</v>
+        <v>268.4154552892337</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37610,28 +37883,28 @@
         <v>0.0561</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1710799003176196</v>
+        <v>0.1736389901260044</v>
       </c>
       <c r="J15" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K15" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1208869184470629</v>
+        <v>0.1258604878820687</v>
       </c>
       <c r="M15" t="n">
-        <v>2.502509008643064</v>
+        <v>2.49578436452298</v>
       </c>
       <c r="N15" t="n">
-        <v>11.97437627076796</v>
+        <v>11.90524419256106</v>
       </c>
       <c r="O15" t="n">
-        <v>3.460401171940612</v>
+        <v>3.450397686145912</v>
       </c>
       <c r="P15" t="n">
-        <v>292.4049027624421</v>
+        <v>292.3789685785334</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37688,28 +37961,28 @@
         <v>0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1252688525510919</v>
+        <v>0.1269236861494812</v>
       </c>
       <c r="J16" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K16" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07285512671112371</v>
+        <v>0.07583521869694365</v>
       </c>
       <c r="M16" t="n">
-        <v>2.442763802618148</v>
+        <v>2.431626066694879</v>
       </c>
       <c r="N16" t="n">
-        <v>11.23474372680561</v>
+        <v>11.1613387239062</v>
       </c>
       <c r="O16" t="n">
-        <v>3.351826923754509</v>
+        <v>3.34085897994905</v>
       </c>
       <c r="P16" t="n">
-        <v>290.5701547127841</v>
+        <v>290.5533973845468</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37766,28 +38039,28 @@
         <v>0.0537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09287552625634306</v>
+        <v>0.09668762307338516</v>
       </c>
       <c r="J17" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K17" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03045967357419788</v>
+        <v>0.03340991327142206</v>
       </c>
       <c r="M17" t="n">
-        <v>2.875554424702778</v>
+        <v>2.873177203409523</v>
       </c>
       <c r="N17" t="n">
-        <v>15.44659273723084</v>
+        <v>15.37663200484862</v>
       </c>
       <c r="O17" t="n">
-        <v>3.930215355070361</v>
+        <v>3.921304885474811</v>
       </c>
       <c r="P17" t="n">
-        <v>285.5279383786003</v>
+        <v>285.4893023496342</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37844,28 +38117,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0715598704800412</v>
+        <v>0.07456003967580173</v>
       </c>
       <c r="J18" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K18" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01345816646287978</v>
+        <v>0.01483430218481718</v>
       </c>
       <c r="M18" t="n">
-        <v>3.049544807400077</v>
+        <v>3.040274969036469</v>
       </c>
       <c r="N18" t="n">
-        <v>21.13032747947351</v>
+        <v>21.00096878956038</v>
       </c>
       <c r="O18" t="n">
-        <v>4.596773594541449</v>
+        <v>4.58268139734374</v>
       </c>
       <c r="P18" t="n">
-        <v>288.8794233073241</v>
+        <v>288.849004763439</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37922,28 +38195,28 @@
         <v>0.0365</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.08278272700715089</v>
+        <v>-0.07971897489591503</v>
       </c>
       <c r="J19" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K19" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01048826974067274</v>
+        <v>0.009902452726918254</v>
       </c>
       <c r="M19" t="n">
-        <v>3.904095609771004</v>
+        <v>3.88633413813641</v>
       </c>
       <c r="N19" t="n">
-        <v>35.81922591849538</v>
+        <v>35.57799421669142</v>
       </c>
       <c r="O19" t="n">
-        <v>5.984916533962306</v>
+        <v>5.964729182175115</v>
       </c>
       <c r="P19" t="n">
-        <v>293.9554573241293</v>
+        <v>293.92404059847</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -38000,28 +38273,28 @@
         <v>0.0659</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1273570917835383</v>
+        <v>-0.1220601932854493</v>
       </c>
       <c r="J20" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K20" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1001361635756413</v>
+        <v>0.09335302031613824</v>
       </c>
       <c r="M20" t="n">
-        <v>2.239551921653563</v>
+        <v>2.248548032958936</v>
       </c>
       <c r="N20" t="n">
-        <v>8.219261587374529</v>
+        <v>8.245317777264509</v>
       </c>
       <c r="O20" t="n">
-        <v>2.866925458984682</v>
+        <v>2.871466137231033</v>
       </c>
       <c r="P20" t="n">
-        <v>275.4334558440759</v>
+        <v>275.3798171966242</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38078,28 +38351,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.05053068604708295</v>
+        <v>-0.03897523412938651</v>
       </c>
       <c r="J21" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K21" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007665594734241554</v>
+        <v>0.00455226324810909</v>
       </c>
       <c r="M21" t="n">
-        <v>3.443505847908368</v>
+        <v>3.477214670071862</v>
       </c>
       <c r="N21" t="n">
-        <v>18.63902834967866</v>
+        <v>18.92857875772929</v>
       </c>
       <c r="O21" t="n">
-        <v>4.317294100438221</v>
+        <v>4.350698651679899</v>
       </c>
       <c r="P21" t="n">
-        <v>248.3151291970838</v>
+        <v>248.1981396833058</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38156,28 +38429,28 @@
         <v>0.1216</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2118873848907697</v>
+        <v>0.2151141568160102</v>
       </c>
       <c r="J22" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K22" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08834044797599994</v>
+        <v>0.09220123371006061</v>
       </c>
       <c r="M22" t="n">
-        <v>3.940822093814128</v>
+        <v>3.928454610119282</v>
       </c>
       <c r="N22" t="n">
-        <v>26.1266650245842</v>
+        <v>25.96212801321737</v>
       </c>
       <c r="O22" t="n">
-        <v>5.111424950499048</v>
+        <v>5.095304506427204</v>
       </c>
       <c r="P22" t="n">
-        <v>222.4628803535529</v>
+        <v>222.4302013377258</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38234,28 +38507,28 @@
         <v>0.0709</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3452677793864077</v>
+        <v>0.3483554079029254</v>
       </c>
       <c r="J23" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K23" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1848466769859219</v>
+        <v>0.1901541095442377</v>
       </c>
       <c r="M23" t="n">
-        <v>4.240438433174731</v>
+        <v>4.222964475879624</v>
       </c>
       <c r="N23" t="n">
-        <v>29.6442484640832</v>
+        <v>29.45040196903001</v>
       </c>
       <c r="O23" t="n">
-        <v>5.444653199615491</v>
+        <v>5.426822456007753</v>
       </c>
       <c r="P23" t="n">
-        <v>235.6060931579813</v>
+        <v>235.5748197609108</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38312,28 +38585,28 @@
         <v>0.0614</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2181198416922118</v>
+        <v>0.2229075063474284</v>
       </c>
       <c r="J24" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K24" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1098876377615922</v>
+        <v>0.1156984571280113</v>
       </c>
       <c r="M24" t="n">
-        <v>3.748001190329892</v>
+        <v>3.748503718120941</v>
       </c>
       <c r="N24" t="n">
-        <v>21.73136611723466</v>
+        <v>21.64071711610018</v>
       </c>
       <c r="O24" t="n">
-        <v>4.661691336546711</v>
+        <v>4.651958417279778</v>
       </c>
       <c r="P24" t="n">
-        <v>268.6982479985712</v>
+        <v>268.6497534730184</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38371,7 +38644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y395"/>
+  <dimension ref="A1:Y398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88503,6 +88776,387 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-38.60771717914963,178.18908375332967</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-38.60784823530357,178.1881525201922</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-38.608105807348046,178.18730967266995</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-38.60837843376813,178.18647734348158</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-38.608649718410796,178.1856440784649</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-38.60897870405218,178.1848511227218</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-38.60941331939837,178.1841319563424</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-38.60996411546278,178.18336572419093</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-38.61052732457796,178.18260814203364</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-38.61112884480356,178.18205410667738</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-38.61168577526918,178.18150615998366</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-38.61222199142781,178.1809196327479</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-38.612764344751405,178.1803445467089</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-38.613443464375315,178.17992168117365</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>-38.614112359026976,178.1794533050881</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>-38.61475929602771,178.17904282080028</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-38.61541473726446,178.17872306565425</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-38.6160636423622,178.17838122406812</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>-38.61666537765223,178.17783123544024</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>-38.61730636226071,178.17728356103902</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>-38.61794765156885,178.1767252198715</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>-38.6186569119707,178.1766470164616</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>-38.61939887741548,178.17672763416857</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-38.60771323778949,178.18908099989258</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-38.60783735709741,178.18814492078428</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-38.60809153949781,178.18729970539567</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-38.60837441352927,178.18647453503962</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-38.60865531523609,178.18564798823343</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-38.608985483330116,178.18485585847714</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-38.60942214825245,178.1841381238301</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-38.60996468210561,178.18336628856645</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-38.61052950168382,178.18261164430763</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-38.61112625610807,178.18204928418544</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-38.61168140999375,178.18149802789026</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-38.61221666169787,178.18090970397589</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>-38.61275490345819,178.18032695850192</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>-38.61343972077217,178.17991319124903</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>-38.614107861464255,178.17943943344721</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>-38.614756062565604,178.1790318847428</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>-38.6154102991596,178.1787080552464</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>-38.616059965056905,178.17836878676465</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>-38.616663177876376,178.1778233550393</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>-38.617300167799655,178.1772570998134</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>-38.617945985172184,178.17671712954277</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>-38.61865558798852,178.17664058846364</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>-38.619397074078506,178.17671887869616</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-38.60770511858733,178.18907532781324</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-38.607830972063056,178.18814046026338</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-38.60808184366523,178.18729293205698</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-38.6083644023458,178.1864675414699</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-38.6086537386656,178.1856468868901</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-38.60898863648255,178.18485806115433</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-38.60942995232846,178.18414357545004</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-38.60996503625739,178.18336664130112</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-38.610535753884534,178.18262170212125</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-38.61113011377184,178.18205647064417</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-38.611684100221694,178.1815030395291</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-38.61221463132432,178.18090592158697</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>-38.612751654840466,178.1803209066468</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>-38.6134420990613,178.1799185848481</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>-38.6141078271317,178.17943932755682</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>-38.61475878881803,178.17904110534022</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>-38.61541169399278,178.17871277280298</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>-38.61606357896039,178.17838100963183</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>-38.61666405176001,178.17782648560947</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>-38.617298471390136,178.17724985317136</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>-38.61794762874149,178.17672510904507</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>-38.618657596788935,178.1766503412882</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>-38.619400269865075,178.1767343947235</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
